--- a/financieras_ratios.xlsx
+++ b/financieras_ratios.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="301">
   <si>
     <t>Calculo</t>
   </si>
@@ -319,715 +319,622 @@
     <t>Entre 80-90 % es bueno, mayor a 100% indica que la empresa esta prestando más de lo que tiene en depósitos y menor a 70% indica que la empresa no esta prestando lo suficiente</t>
   </si>
   <si>
-    <t>30.37</t>
+    <t>6.98</t>
+  </si>
+  <si>
+    <t>1.71</t>
+  </si>
+  <si>
+    <t>24.57</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>2.99</t>
+  </si>
+  <si>
+    <t>0.30</t>
+  </si>
+  <si>
+    <t>1.93</t>
+  </si>
+  <si>
+    <t>0.89</t>
+  </si>
+  <si>
+    <t>8.79</t>
+  </si>
+  <si>
+    <t>29.88</t>
+  </si>
+  <si>
+    <t>9.79</t>
+  </si>
+  <si>
+    <t>0.00</t>
+  </si>
+  <si>
+    <t>6.33</t>
+  </si>
+  <si>
+    <t>1.97</t>
+  </si>
+  <si>
+    <t>31.12</t>
+  </si>
+  <si>
+    <t>6.13</t>
+  </si>
+  <si>
+    <t>0.60</t>
+  </si>
+  <si>
+    <t>0.62</t>
+  </si>
+  <si>
+    <t>7.44</t>
+  </si>
+  <si>
+    <t>37.70</t>
+  </si>
+  <si>
+    <t>8.44</t>
+  </si>
+  <si>
+    <t>-24.74</t>
+  </si>
+  <si>
+    <t>1.53</t>
+  </si>
+  <si>
+    <t>0.52</t>
+  </si>
+  <si>
+    <t>34.25</t>
+  </si>
+  <si>
+    <t>7.32</t>
+  </si>
+  <si>
+    <t>0.59</t>
+  </si>
+  <si>
+    <t>7.69</t>
+  </si>
+  <si>
+    <t>0.14</t>
+  </si>
+  <si>
+    <t>10.51</t>
+  </si>
+  <si>
+    <t>58.09</t>
+  </si>
+  <si>
+    <t>11.51</t>
+  </si>
+  <si>
+    <t>27.99</t>
+  </si>
+  <si>
+    <t>7.07</t>
+  </si>
+  <si>
+    <t>2.36</t>
+  </si>
+  <si>
+    <t>33.44</t>
+  </si>
+  <si>
+    <t>2.38</t>
+  </si>
+  <si>
+    <t>0.17</t>
+  </si>
+  <si>
+    <t>1.69</t>
+  </si>
+  <si>
+    <t>0.53</t>
+  </si>
+  <si>
+    <t>6.92</t>
+  </si>
+  <si>
+    <t>44.87</t>
+  </si>
+  <si>
+    <t>7.92</t>
+  </si>
+  <si>
+    <t>6.93</t>
+  </si>
+  <si>
+    <t>6.07</t>
+  </si>
+  <si>
+    <t>2.32</t>
+  </si>
+  <si>
+    <t>38.27</t>
+  </si>
+  <si>
+    <t>6.85</t>
+  </si>
+  <si>
+    <t>0.51</t>
+  </si>
+  <si>
+    <t>1.72</t>
+  </si>
+  <si>
+    <t>0.56</t>
+  </si>
+  <si>
+    <t>5.86</t>
+  </si>
+  <si>
+    <t>34.34</t>
+  </si>
+  <si>
+    <t>6.86</t>
+  </si>
+  <si>
+    <t>-9.39</t>
+  </si>
+  <si>
+    <t>5.82</t>
   </si>
   <si>
     <t>2.30</t>
   </si>
   <si>
-    <t>7.57</t>
-  </si>
-  <si>
-    <t>19.78</t>
-  </si>
-  <si>
-    <t>0.05</t>
-  </si>
-  <si>
-    <t>92.17</t>
-  </si>
-  <si>
-    <t>0.14</t>
-  </si>
-  <si>
-    <t>9.79</t>
-  </si>
-  <si>
-    <t>108.31</t>
-  </si>
-  <si>
-    <t>10.79</t>
-  </si>
-  <si>
-    <t>0.00</t>
-  </si>
-  <si>
-    <t>50.28</t>
-  </si>
-  <si>
-    <t>97.45</t>
-  </si>
-  <si>
-    <t>23.87</t>
-  </si>
-  <si>
-    <t>1.68</t>
-  </si>
-  <si>
-    <t>7.03</t>
-  </si>
-  <si>
-    <t>14.17</t>
-  </si>
-  <si>
-    <t>0.02</t>
-  </si>
-  <si>
-    <t>142.86</t>
+    <t>39.44</t>
+  </si>
+  <si>
+    <t>4.94</t>
+  </si>
+  <si>
+    <t>0.21</t>
+  </si>
+  <si>
+    <t>1.74</t>
+  </si>
+  <si>
+    <t>0.25</t>
+  </si>
+  <si>
+    <t>5.34</t>
+  </si>
+  <si>
+    <t>62.42</t>
+  </si>
+  <si>
+    <t>6.34</t>
+  </si>
+  <si>
+    <t>-51.01</t>
+  </si>
+  <si>
+    <t>5.57</t>
+  </si>
+  <si>
+    <t>2.80</t>
+  </si>
+  <si>
+    <t>50.29</t>
+  </si>
+  <si>
+    <t>6.67</t>
+  </si>
+  <si>
+    <t>0.37</t>
+  </si>
+  <si>
+    <t>1.43</t>
+  </si>
+  <si>
+    <t>0.33</t>
+  </si>
+  <si>
+    <t>4.44</t>
+  </si>
+  <si>
+    <t>50.45</t>
+  </si>
+  <si>
+    <t>5.44</t>
+  </si>
+  <si>
+    <t>-29.03</t>
+  </si>
+  <si>
+    <t>4.56</t>
+  </si>
+  <si>
+    <t>2.59</t>
+  </si>
+  <si>
+    <t>56.87</t>
+  </si>
+  <si>
+    <t>0.04</t>
+  </si>
+  <si>
+    <t>1.54</t>
+  </si>
+  <si>
+    <t>0.29</t>
+  </si>
+  <si>
+    <t>4.09</t>
+  </si>
+  <si>
+    <t>46.96</t>
+  </si>
+  <si>
+    <t>5.09</t>
+  </si>
+  <si>
+    <t>71.24</t>
+  </si>
+  <si>
+    <t>6.02</t>
+  </si>
+  <si>
+    <t>3.91</t>
+  </si>
+  <si>
+    <t>64.99</t>
+  </si>
+  <si>
+    <t>4.83</t>
+  </si>
+  <si>
+    <t>1.02</t>
+  </si>
+  <si>
+    <t>0.42</t>
+  </si>
+  <si>
+    <t>4.14</t>
+  </si>
+  <si>
+    <t>45.77</t>
+  </si>
+  <si>
+    <t>5.14</t>
+  </si>
+  <si>
+    <t>-16.18</t>
+  </si>
+  <si>
+    <t>5.53</t>
+  </si>
+  <si>
+    <t>4.02</t>
+  </si>
+  <si>
+    <t>72.67</t>
+  </si>
+  <si>
+    <t>6.40</t>
+  </si>
+  <si>
+    <t>0.47</t>
+  </si>
+  <si>
+    <t>1.00</t>
+  </si>
+  <si>
+    <t>3.71</t>
+  </si>
+  <si>
+    <t>41.44</t>
+  </si>
+  <si>
+    <t>4.71</t>
+  </si>
+  <si>
+    <t>-32.54</t>
+  </si>
+  <si>
+    <t>4.67</t>
+  </si>
+  <si>
+    <t>3.60</t>
+  </si>
+  <si>
+    <t>77.04</t>
+  </si>
+  <si>
+    <t>8.91</t>
+  </si>
+  <si>
+    <t>0.71</t>
+  </si>
+  <si>
+    <t>1.11</t>
+  </si>
+  <si>
+    <t>0.39</t>
+  </si>
+  <si>
+    <t>3.31</t>
+  </si>
+  <si>
+    <t>34.50</t>
+  </si>
+  <si>
+    <t>4.31</t>
+  </si>
+  <si>
+    <t>13.62</t>
+  </si>
+  <si>
+    <t>5.32</t>
+  </si>
+  <si>
+    <t>4.39</t>
+  </si>
+  <si>
+    <t>82.41</t>
+  </si>
+  <si>
+    <t>8.60</t>
+  </si>
+  <si>
+    <t>0.66</t>
+  </si>
+  <si>
+    <t>0.91</t>
+  </si>
+  <si>
+    <t>0.43</t>
+  </si>
+  <si>
+    <t>3.49</t>
+  </si>
+  <si>
+    <t>37.78</t>
+  </si>
+  <si>
+    <t>4.49</t>
+  </si>
+  <si>
+    <t>4.32</t>
+  </si>
+  <si>
+    <t>5.43</t>
+  </si>
+  <si>
+    <t>5.35</t>
+  </si>
+  <si>
+    <t>98.46</t>
+  </si>
+  <si>
+    <t>6.68</t>
   </si>
   <si>
     <t>0.08</t>
   </si>
   <si>
-    <t>10.69</t>
-  </si>
-  <si>
-    <t>134.54</t>
-  </si>
-  <si>
-    <t>11.69</t>
-  </si>
-  <si>
-    <t>2.93</t>
-  </si>
-  <si>
-    <t>59.13</t>
-  </si>
-  <si>
-    <t>108.90</t>
-  </si>
-  <si>
-    <t>5.55</t>
-  </si>
-  <si>
-    <t>0.44</t>
-  </si>
-  <si>
-    <t>7.86</t>
-  </si>
-  <si>
-    <t>2.68</t>
-  </si>
-  <si>
-    <t>509.09</t>
-  </si>
-  <si>
-    <t>0.01</t>
-  </si>
-  <si>
-    <t>9.27</t>
-  </si>
-  <si>
-    <t>151.53</t>
-  </si>
-  <si>
-    <t>10.27</t>
-  </si>
-  <si>
-    <t>-2.85</t>
-  </si>
-  <si>
-    <t>56.19</t>
-  </si>
-  <si>
-    <t>104.00</t>
-  </si>
-  <si>
-    <t>5.72</t>
-  </si>
-  <si>
-    <t>0.41</t>
-  </si>
-  <si>
-    <t>7.09</t>
-  </si>
-  <si>
-    <t>116.29</t>
-  </si>
-  <si>
-    <t>0.25</t>
-  </si>
-  <si>
-    <t>9.76</t>
-  </si>
-  <si>
-    <t>8.64</t>
-  </si>
-  <si>
-    <t>189.47</t>
-  </si>
-  <si>
-    <t>9.64</t>
-  </si>
-  <si>
-    <t>-6.95</t>
-  </si>
-  <si>
-    <t>58.37</t>
-  </si>
-  <si>
-    <t>89.34</t>
-  </si>
-  <si>
-    <t>-2.13</t>
-  </si>
-  <si>
-    <t>-0.11</t>
-  </si>
-  <si>
-    <t>5.36</t>
-  </si>
-  <si>
-    <t>77.70</t>
+    <t>0.75</t>
+  </si>
+  <si>
+    <t>0.07</t>
+  </si>
+  <si>
+    <t>2.73</t>
+  </si>
+  <si>
+    <t>96.23</t>
+  </si>
+  <si>
+    <t>3.73</t>
+  </si>
+  <si>
+    <t>82.99</t>
+  </si>
+  <si>
+    <t>3.32</t>
+  </si>
+  <si>
+    <t>6.72</t>
+  </si>
+  <si>
+    <t>202.39</t>
+  </si>
+  <si>
+    <t>5.49</t>
+  </si>
+  <si>
+    <t>0.23</t>
   </si>
   <si>
     <t>0.16</t>
   </si>
   <si>
-    <t>-36.36</t>
-  </si>
-  <si>
-    <t>-0.00</t>
-  </si>
-  <si>
-    <t>8.92</t>
-  </si>
-  <si>
-    <t>196.47</t>
-  </si>
-  <si>
-    <t>9.92</t>
-  </si>
-  <si>
-    <t>-18.67</t>
-  </si>
-  <si>
-    <t>65.63</t>
-  </si>
-  <si>
-    <t>90.37</t>
-  </si>
-  <si>
-    <t>0.07</t>
-  </si>
-  <si>
-    <t>4.20</t>
-  </si>
-  <si>
-    <t>73.34</t>
-  </si>
-  <si>
-    <t>0.15</t>
-  </si>
-  <si>
-    <t>57.14</t>
-  </si>
-  <si>
-    <t>8.25</t>
-  </si>
-  <si>
-    <t>161.78</t>
-  </si>
-  <si>
-    <t>9.25</t>
-  </si>
-  <si>
-    <t>-69.30</t>
-  </si>
-  <si>
-    <t>88.80</t>
-  </si>
-  <si>
-    <t>85.82</t>
-  </si>
-  <si>
-    <t>5.15</t>
-  </si>
-  <si>
-    <t>0.19</t>
-  </si>
-  <si>
-    <t>3.75</t>
-  </si>
-  <si>
-    <t>-19.76</t>
-  </si>
-  <si>
-    <t>-0.05</t>
-  </si>
-  <si>
-    <t>21.05</t>
-  </si>
-  <si>
-    <t>8.33</t>
-  </si>
-  <si>
-    <t>116.30</t>
-  </si>
-  <si>
-    <t>9.33</t>
-  </si>
-  <si>
-    <t>215.42</t>
-  </si>
-  <si>
-    <t>83.55</t>
-  </si>
-  <si>
-    <t>79.55</t>
-  </si>
-  <si>
-    <t>13.29</t>
-  </si>
-  <si>
-    <t>0.50</t>
-  </si>
-  <si>
-    <t>3.74</t>
-  </si>
-  <si>
-    <t>107.27</t>
-  </si>
-  <si>
-    <t>0.31</t>
-  </si>
-  <si>
-    <t>8.00</t>
-  </si>
-  <si>
-    <t>8.03</t>
-  </si>
-  <si>
-    <t>107.30</t>
-  </si>
-  <si>
-    <t>9.03</t>
-  </si>
-  <si>
-    <t>12.30</t>
-  </si>
-  <si>
-    <t>80.44</t>
-  </si>
-  <si>
-    <t>80.15</t>
-  </si>
-  <si>
-    <t>6.43</t>
-  </si>
-  <si>
-    <t>0.26</t>
-  </si>
-  <si>
-    <t>4.06</t>
-  </si>
-  <si>
-    <t>34.50</t>
-  </si>
-  <si>
-    <t>0.11</t>
-  </si>
-  <si>
-    <t>46.15</t>
-  </si>
-  <si>
-    <t>7.64</t>
-  </si>
-  <si>
-    <t>99.86</t>
-  </si>
-  <si>
-    <t>-25.86</t>
-  </si>
-  <si>
-    <t>88.08</t>
-  </si>
-  <si>
-    <t>76.42</t>
-  </si>
-  <si>
-    <t>19.18</t>
-  </si>
-  <si>
-    <t>0.71</t>
-  </si>
-  <si>
-    <t>3.69</t>
-  </si>
-  <si>
-    <t>34.23</t>
-  </si>
-  <si>
-    <t>28.17</t>
-  </si>
-  <si>
-    <t>7.37</t>
-  </si>
-  <si>
-    <t>92.42</t>
-  </si>
-  <si>
-    <t>8.37</t>
-  </si>
-  <si>
-    <t>-15.12</t>
-  </si>
-  <si>
-    <t>69.45</t>
-  </si>
-  <si>
-    <t>72.80</t>
-  </si>
-  <si>
-    <t>21.29</t>
-  </si>
-  <si>
-    <t>0.81</t>
-  </si>
-  <si>
-    <t>3.79</t>
-  </si>
-  <si>
-    <t>20.64</t>
-  </si>
-  <si>
-    <t>30.86</t>
-  </si>
-  <si>
-    <t>7.22</t>
-  </si>
-  <si>
-    <t>81.45</t>
-  </si>
-  <si>
-    <t>8.22</t>
-  </si>
-  <si>
-    <t>31.87</t>
-  </si>
-  <si>
-    <t>65.81</t>
-  </si>
-  <si>
-    <t>69.95</t>
-  </si>
-  <si>
-    <t>20.93</t>
-  </si>
-  <si>
-    <t>0.85</t>
-  </si>
-  <si>
-    <t>4.04</t>
-  </si>
-  <si>
-    <t>11.32</t>
-  </si>
-  <si>
-    <t>0.04</t>
-  </si>
-  <si>
-    <t>45.88</t>
-  </si>
-  <si>
-    <t>7.54</t>
-  </si>
-  <si>
-    <t>85.12</t>
-  </si>
-  <si>
-    <t>8.54</t>
-  </si>
-  <si>
-    <t>33.86</t>
-  </si>
-  <si>
-    <t>62.57</t>
-  </si>
-  <si>
-    <t>69.93</t>
-  </si>
-  <si>
-    <t>30.92</t>
-  </si>
-  <si>
-    <t>1.37</t>
-  </si>
-  <si>
-    <t>4.45</t>
-  </si>
-  <si>
-    <t>43.42</t>
-  </si>
-  <si>
-    <t>39.42</t>
+    <t>2.43</t>
+  </si>
+  <si>
+    <t>70.28</t>
+  </si>
+  <si>
+    <t>3.43</t>
+  </si>
+  <si>
+    <t>-18.34</t>
+  </si>
+  <si>
+    <t>5.27</t>
+  </si>
+  <si>
+    <t>11.48</t>
+  </si>
+  <si>
+    <t>217.91</t>
+  </si>
+  <si>
+    <t>5.77</t>
+  </si>
+  <si>
+    <t>0.28</t>
+  </si>
+  <si>
+    <t>0.35</t>
+  </si>
+  <si>
+    <t>2.09</t>
+  </si>
+  <si>
+    <t>58.64</t>
+  </si>
+  <si>
+    <t>3.09</t>
+  </si>
+  <si>
+    <t>-21.23</t>
+  </si>
+  <si>
+    <t>3.08</t>
+  </si>
+  <si>
+    <t>7.87</t>
+  </si>
+  <si>
+    <t>255.55</t>
+  </si>
+  <si>
+    <t>3.46</t>
+  </si>
+  <si>
+    <t>0.18</t>
+  </si>
+  <si>
+    <t>50.83</t>
+  </si>
+  <si>
+    <t>2.28</t>
+  </si>
+  <si>
+    <t>65.97</t>
+  </si>
+  <si>
+    <t>3.28</t>
+  </si>
+  <si>
+    <t>10.16</t>
+  </si>
+  <si>
+    <t>3.72</t>
+  </si>
+  <si>
+    <t>10.71</t>
+  </si>
+  <si>
+    <t>287.53</t>
+  </si>
+  <si>
+    <t>0.24</t>
+  </si>
+  <si>
+    <t>41.83</t>
+  </si>
+  <si>
+    <t>2.22</t>
+  </si>
+  <si>
+    <t>62.79</t>
+  </si>
+  <si>
+    <t>3.22</t>
+  </si>
+  <si>
+    <t>13.12</t>
+  </si>
+  <si>
+    <t>2.65</t>
+  </si>
+  <si>
+    <t>8.70</t>
+  </si>
+  <si>
+    <t>328.73</t>
+  </si>
+  <si>
+    <t>5.25</t>
+  </si>
+  <si>
+    <t>56.55</t>
+  </si>
+  <si>
+    <t>60.74</t>
+  </si>
+  <si>
+    <t>3.30</t>
+  </si>
+  <si>
+    <t>-16.14</t>
+  </si>
+  <si>
+    <t>1.41</t>
+  </si>
+  <si>
+    <t>6.06</t>
+  </si>
+  <si>
+    <t>431.44</t>
+  </si>
+  <si>
+    <t>3.67</t>
+  </si>
+  <si>
+    <t>92.41</t>
   </si>
   <si>
     <t>0.12</t>
   </si>
   <si>
-    <t>7.87</t>
-  </si>
-  <si>
-    <t>86.46</t>
-  </si>
-  <si>
-    <t>8.87</t>
-  </si>
-  <si>
-    <t>7.13</t>
-  </si>
-  <si>
-    <t>58.40</t>
-  </si>
-  <si>
-    <t>66.98</t>
-  </si>
-  <si>
-    <t>30.06</t>
-  </si>
-  <si>
-    <t>1.45</t>
-  </si>
-  <si>
-    <t>4.83</t>
-  </si>
-  <si>
-    <t>67.71</t>
-  </si>
-  <si>
-    <t>0.23</t>
-  </si>
-  <si>
-    <t>45.52</t>
-  </si>
-  <si>
-    <t>8.19</t>
-  </si>
-  <si>
-    <t>90.95</t>
-  </si>
-  <si>
-    <t>9.19</t>
-  </si>
-  <si>
-    <t>5.43</t>
-  </si>
-  <si>
-    <t>60.17</t>
-  </si>
-  <si>
-    <t>67.15</t>
-  </si>
-  <si>
-    <t>20.92</t>
-  </si>
-  <si>
-    <t>1.02</t>
-  </si>
-  <si>
-    <t>4.86</t>
-  </si>
-  <si>
-    <t>44.42</t>
-  </si>
-  <si>
-    <t>0.13</t>
-  </si>
-  <si>
-    <t>70.59</t>
-  </si>
-  <si>
-    <t>96.34</t>
-  </si>
-  <si>
-    <t>10.33</t>
-  </si>
-  <si>
-    <t>-34.17</t>
-  </si>
-  <si>
-    <t>64.56</t>
-  </si>
-  <si>
-    <t>50.20</t>
-  </si>
-  <si>
-    <t>35.88</t>
-  </si>
-  <si>
-    <t>1.87</t>
-  </si>
-  <si>
-    <t>5.21</t>
-  </si>
-  <si>
-    <t>-8.07</t>
-  </si>
-  <si>
-    <t>-0.02</t>
-  </si>
-  <si>
-    <t>41.71</t>
-  </si>
-  <si>
-    <t>10.74</t>
-  </si>
-  <si>
-    <t>103.72</t>
-  </si>
-  <si>
-    <t>11.74</t>
-  </si>
-  <si>
-    <t>5.91</t>
-  </si>
-  <si>
-    <t>67.03</t>
-  </si>
-  <si>
-    <t>46.87</t>
-  </si>
-  <si>
-    <t>28.99</t>
-  </si>
-  <si>
-    <t>1.69</t>
-  </si>
-  <si>
-    <t>5.81</t>
-  </si>
-  <si>
-    <t>-6.66</t>
-  </si>
-  <si>
-    <t>50.89</t>
-  </si>
-  <si>
-    <t>0.10</t>
-  </si>
-  <si>
-    <t>10.17</t>
-  </si>
-  <si>
-    <t>101.02</t>
-  </si>
-  <si>
-    <t>11.17</t>
-  </si>
-  <si>
-    <t>31.83</t>
-  </si>
-  <si>
-    <t>64.71</t>
-  </si>
-  <si>
-    <t>53.17</t>
-  </si>
-  <si>
-    <t>26.90</t>
-  </si>
-  <si>
-    <t>1.64</t>
-  </si>
-  <si>
-    <t>6.10</t>
-  </si>
-  <si>
-    <t>45.63</t>
-  </si>
-  <si>
-    <t>56.10</t>
-  </si>
-  <si>
-    <t>0.09</t>
-  </si>
-  <si>
-    <t>9.90</t>
-  </si>
-  <si>
-    <t>103.62</t>
-  </si>
-  <si>
-    <t>10.90</t>
-  </si>
-  <si>
-    <t>91.42</t>
-  </si>
-  <si>
-    <t>64.66</t>
-  </si>
-  <si>
-    <t>53.62</t>
-  </si>
-  <si>
-    <t>26.63</t>
-  </si>
-  <si>
-    <t>1.71</t>
-  </si>
-  <si>
-    <t>6.42</t>
-  </si>
-  <si>
-    <t>-8.64</t>
-  </si>
-  <si>
-    <t>-0.03</t>
-  </si>
-  <si>
-    <t>58.48</t>
-  </si>
-  <si>
-    <t>10.04</t>
-  </si>
-  <si>
-    <t>95.85</t>
-  </si>
-  <si>
-    <t>11.04</t>
-  </si>
-  <si>
-    <t>11.84</t>
-  </si>
-  <si>
-    <t>65.57</t>
-  </si>
-  <si>
-    <t>54.77</t>
-  </si>
-  <si>
-    <t>27.64</t>
-  </si>
-  <si>
-    <t>1.94</t>
-  </si>
-  <si>
-    <t>57.31</t>
-  </si>
-  <si>
-    <t>0.17</t>
-  </si>
-  <si>
-    <t>54.64</t>
-  </si>
-  <si>
-    <t>10.19</t>
-  </si>
-  <si>
-    <t>102.41</t>
-  </si>
-  <si>
-    <t>11.19</t>
-  </si>
-  <si>
-    <t>-10.53</t>
-  </si>
-  <si>
-    <t>64.40</t>
-  </si>
-  <si>
-    <t>57.10</t>
+    <t>2.78</t>
+  </si>
+  <si>
+    <t>70.16</t>
+  </si>
+  <si>
+    <t>3.78</t>
+  </si>
+  <si>
+    <t>2.29</t>
+  </si>
+  <si>
+    <t>11.49</t>
+  </si>
+  <si>
+    <t>500.75</t>
+  </si>
+  <si>
+    <t>0.22</t>
+  </si>
+  <si>
+    <t>51.61</t>
+  </si>
+  <si>
+    <t>0.20</t>
+  </si>
+  <si>
+    <t>2.76</t>
+  </si>
+  <si>
+    <t>73.66</t>
+  </si>
+  <si>
+    <t>3.76</t>
+  </si>
+  <si>
+    <t>-24.30</t>
   </si>
 </sst>
 </file>
@@ -1470,61 +1377,61 @@
         <v>95</v>
       </c>
       <c r="E2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F2" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G2" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="H2" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="I2" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
       <c r="J2" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="K2" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="L2" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="M2" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="N2" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="O2" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="P2" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="Q2" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="R2" t="s">
-        <v>262</v>
+        <v>245</v>
       </c>
       <c r="S2" t="s">
-        <v>273</v>
+        <v>255</v>
       </c>
       <c r="T2" t="s">
-        <v>285</v>
+        <v>265</v>
       </c>
       <c r="U2" t="s">
-        <v>297</v>
+        <v>274</v>
       </c>
       <c r="V2" t="s">
-        <v>309</v>
+        <v>282</v>
       </c>
       <c r="W2" t="s">
-        <v>321</v>
+        <v>291</v>
       </c>
     </row>
     <row r="3" spans="1:23">
@@ -1541,61 +1448,61 @@
         <v>96</v>
       </c>
       <c r="E3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F3" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="G3" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="H3" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="I3" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="J3" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="K3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="L3" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="M3" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="N3" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="O3" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="P3" t="s">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="Q3" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="R3" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="S3" t="s">
-        <v>274</v>
+        <v>256</v>
       </c>
       <c r="T3" t="s">
-        <v>286</v>
+        <v>266</v>
       </c>
       <c r="U3" t="s">
-        <v>298</v>
+        <v>275</v>
       </c>
       <c r="V3" t="s">
-        <v>310</v>
+        <v>283</v>
       </c>
       <c r="W3" t="s">
-        <v>322</v>
+        <v>292</v>
       </c>
     </row>
     <row r="4" spans="1:23">
@@ -1612,61 +1519,61 @@
         <v>97</v>
       </c>
       <c r="E4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F4" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="G4" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="H4" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="I4" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="J4" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="K4" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="L4" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="M4" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="N4" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="O4" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="P4" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="Q4" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="R4" t="s">
-        <v>264</v>
+        <v>247</v>
       </c>
       <c r="S4" t="s">
-        <v>275</v>
+        <v>257</v>
       </c>
       <c r="T4" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="U4" t="s">
-        <v>299</v>
+        <v>276</v>
       </c>
       <c r="V4" t="s">
-        <v>311</v>
+        <v>284</v>
       </c>
       <c r="W4" t="s">
-        <v>110</v>
+        <v>293</v>
       </c>
     </row>
     <row r="5" spans="1:23">
@@ -1677,64 +1584,64 @@
         <v>71</v>
       </c>
       <c r="D5">
-        <v>4595.896</v>
+        <v>336.735</v>
       </c>
       <c r="E5">
-        <v>4463.213</v>
+        <v>283.191</v>
       </c>
       <c r="F5">
-        <v>4596.428</v>
+        <v>278.843</v>
       </c>
       <c r="G5">
-        <v>7728.57</v>
+        <v>275.357</v>
       </c>
       <c r="H5">
-        <v>9790.472</v>
+        <v>275.287</v>
       </c>
       <c r="I5">
-        <v>10254.824</v>
+        <v>274.249</v>
       </c>
       <c r="J5">
-        <v>10840.854</v>
+        <v>289.53</v>
       </c>
       <c r="K5">
-        <v>11491.418</v>
+        <v>284.685</v>
       </c>
       <c r="L5">
-        <v>10584.535</v>
+        <v>268.603</v>
       </c>
       <c r="M5">
-        <v>11236.23</v>
+        <v>260.592</v>
       </c>
       <c r="N5">
-        <v>11046.8</v>
+        <v>259.647</v>
       </c>
       <c r="O5">
-        <v>10778.4</v>
+        <v>255.072</v>
       </c>
       <c r="P5">
-        <v>10236.9</v>
+        <v>246.652</v>
       </c>
       <c r="Q5">
-        <v>9442.9</v>
+        <v>379.817</v>
       </c>
       <c r="R5">
-        <v>8796.9</v>
+        <v>368.389</v>
       </c>
       <c r="S5">
-        <v>8558.4</v>
+        <v>340.966</v>
       </c>
       <c r="T5">
-        <v>8167.5</v>
+        <v>313.065</v>
       </c>
       <c r="U5">
-        <v>8080.5</v>
+        <v>296.882</v>
       </c>
       <c r="V5">
-        <v>7935.8</v>
+        <v>283.218</v>
       </c>
       <c r="W5">
-        <v>7627.1</v>
+        <v>267.53</v>
       </c>
     </row>
     <row r="6" spans="1:23">
@@ -1744,65 +1651,65 @@
       <c r="C6" t="s">
         <v>72</v>
       </c>
-      <c r="D6">
-        <v>3.14</v>
-      </c>
-      <c r="E6">
-        <v>2.71</v>
-      </c>
-      <c r="F6">
-        <v>3.25</v>
-      </c>
-      <c r="G6">
-        <v>3.16</v>
-      </c>
-      <c r="H6">
-        <v>3.2</v>
-      </c>
-      <c r="I6">
-        <v>2.76</v>
-      </c>
-      <c r="J6">
-        <v>2.49</v>
-      </c>
-      <c r="K6">
-        <v>2.65</v>
-      </c>
-      <c r="L6">
-        <v>2.71</v>
-      </c>
-      <c r="M6">
-        <v>2.56</v>
-      </c>
-      <c r="N6">
-        <v>2.63</v>
-      </c>
-      <c r="O6">
-        <v>2.78</v>
-      </c>
-      <c r="P6">
-        <v>2.84</v>
-      </c>
-      <c r="Q6">
-        <v>2.74</v>
-      </c>
-      <c r="R6">
-        <v>2.25</v>
-      </c>
-      <c r="S6">
-        <v>1.98</v>
-      </c>
-      <c r="T6">
-        <v>2.24</v>
-      </c>
-      <c r="U6">
-        <v>2.44</v>
-      </c>
-      <c r="V6">
-        <v>2.36</v>
-      </c>
-      <c r="W6">
-        <v>2.34</v>
+      <c r="D6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E6" t="s">
+        <v>98</v>
+      </c>
+      <c r="F6" t="s">
+        <v>98</v>
+      </c>
+      <c r="G6" t="s">
+        <v>98</v>
+      </c>
+      <c r="H6" t="s">
+        <v>98</v>
+      </c>
+      <c r="I6" t="s">
+        <v>98</v>
+      </c>
+      <c r="J6" t="s">
+        <v>98</v>
+      </c>
+      <c r="K6" t="s">
+        <v>98</v>
+      </c>
+      <c r="L6" t="s">
+        <v>98</v>
+      </c>
+      <c r="M6" t="s">
+        <v>98</v>
+      </c>
+      <c r="N6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O6" t="s">
+        <v>98</v>
+      </c>
+      <c r="P6" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>98</v>
+      </c>
+      <c r="R6" t="s">
+        <v>98</v>
+      </c>
+      <c r="S6" t="s">
+        <v>98</v>
+      </c>
+      <c r="T6" t="s">
+        <v>98</v>
+      </c>
+      <c r="U6" t="s">
+        <v>98</v>
+      </c>
+      <c r="V6" t="s">
+        <v>98</v>
+      </c>
+      <c r="W6" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="7" spans="1:23">
@@ -1813,13 +1720,13 @@
         <v>73</v>
       </c>
       <c r="D7">
-        <v>2.12</v>
+        <v>0.033</v>
       </c>
       <c r="E7">
-        <v>2.4</v>
+        <v>0.038</v>
       </c>
       <c r="F7">
-        <v>2.24</v>
+        <v>0.04</v>
       </c>
       <c r="G7">
         <v>0.04</v>
@@ -1837,40 +1744,40 @@
         <v>0.04</v>
       </c>
       <c r="L7">
-        <v>0.12</v>
+        <v>0.04</v>
       </c>
       <c r="M7">
-        <v>0.2</v>
+        <v>0.04</v>
       </c>
       <c r="N7">
-        <v>0.25</v>
+        <v>0.04</v>
       </c>
       <c r="O7">
-        <v>0.39</v>
+        <v>0.04</v>
       </c>
       <c r="P7">
-        <v>0.54</v>
+        <v>0.04</v>
       </c>
       <c r="Q7">
-        <v>0.66</v>
+        <v>0.04</v>
       </c>
       <c r="R7">
-        <v>0.72</v>
+        <v>0.04</v>
       </c>
       <c r="S7">
-        <v>0.78</v>
+        <v>4</v>
       </c>
       <c r="T7">
-        <v>0.86</v>
+        <v>4.48</v>
       </c>
       <c r="U7">
-        <v>0.92</v>
+        <v>4.92</v>
       </c>
       <c r="V7">
-        <v>1</v>
+        <v>5.6</v>
       </c>
       <c r="W7">
-        <v>1.06</v>
+        <v>5.93</v>
       </c>
     </row>
     <row r="8" spans="1:23">
@@ -1884,64 +1791,64 @@
         <v>74</v>
       </c>
       <c r="D8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F8" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="G8" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="H8" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="I8" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="J8" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="K8" t="s">
-        <v>184</v>
+        <v>121</v>
       </c>
       <c r="L8" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="M8" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="N8" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="O8" t="s">
-        <v>229</v>
+        <v>216</v>
       </c>
       <c r="P8" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="Q8" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
       <c r="R8" t="s">
-        <v>265</v>
+        <v>248</v>
       </c>
       <c r="S8" t="s">
-        <v>276</v>
+        <v>258</v>
       </c>
       <c r="T8" t="s">
+        <v>178</v>
+      </c>
+      <c r="U8" t="s">
+        <v>277</v>
+      </c>
+      <c r="V8" t="s">
+        <v>285</v>
+      </c>
+      <c r="W8" t="s">
         <v>288</v>
-      </c>
-      <c r="U8" t="s">
-        <v>300</v>
-      </c>
-      <c r="V8" t="s">
-        <v>312</v>
-      </c>
-      <c r="W8" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="9" spans="1:23">
@@ -1955,64 +1862,64 @@
         <v>75</v>
       </c>
       <c r="D9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F9" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="G9" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="H9" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="I9" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="J9" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="K9" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="L9" t="s">
-        <v>197</v>
+        <v>167</v>
       </c>
       <c r="M9" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="N9" t="s">
-        <v>158</v>
+        <v>206</v>
       </c>
       <c r="O9" t="s">
-        <v>230</v>
+        <v>217</v>
       </c>
       <c r="P9" t="s">
-        <v>149</v>
+        <v>228</v>
       </c>
       <c r="Q9" t="s">
-        <v>254</v>
+        <v>239</v>
       </c>
       <c r="R9" t="s">
-        <v>266</v>
+        <v>249</v>
       </c>
       <c r="S9" t="s">
-        <v>277</v>
+        <v>259</v>
       </c>
       <c r="T9" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="U9" t="s">
-        <v>266</v>
+        <v>167</v>
       </c>
       <c r="V9" t="s">
-        <v>313</v>
+        <v>249</v>
       </c>
       <c r="W9" t="s">
-        <v>324</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10" spans="1:23">
@@ -2026,64 +1933,64 @@
         <v>76</v>
       </c>
       <c r="D10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E10" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="F10" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="G10" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="H10" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="I10" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="J10" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="K10" t="s">
+        <v>176</v>
+      </c>
+      <c r="L10" t="s">
         <v>186</v>
       </c>
-      <c r="L10" t="s">
-        <v>198</v>
-      </c>
       <c r="M10" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="N10" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="O10" t="s">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="P10" t="s">
-        <v>242</v>
+        <v>229</v>
       </c>
       <c r="Q10" t="s">
-        <v>255</v>
+        <v>111</v>
       </c>
       <c r="R10" t="s">
-        <v>267</v>
+        <v>250</v>
       </c>
       <c r="S10" t="s">
+        <v>260</v>
+      </c>
+      <c r="T10" t="s">
+        <v>269</v>
+      </c>
+      <c r="U10" t="s">
         <v>278</v>
       </c>
-      <c r="T10" t="s">
-        <v>289</v>
-      </c>
-      <c r="U10" t="s">
-        <v>301</v>
-      </c>
       <c r="V10" t="s">
-        <v>314</v>
+        <v>286</v>
       </c>
       <c r="W10" t="s">
-        <v>325</v>
+        <v>295</v>
       </c>
     </row>
     <row r="11" spans="1:23">
@@ -2097,64 +2004,64 @@
         <v>77</v>
       </c>
       <c r="D11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E11" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F11" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="G11" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="H11" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="I11" t="s">
-        <v>105</v>
+        <v>156</v>
       </c>
       <c r="J11" t="s">
-        <v>112</v>
+        <v>167</v>
       </c>
       <c r="K11" t="s">
-        <v>99</v>
+        <v>177</v>
       </c>
       <c r="L11" t="s">
-        <v>112</v>
+        <v>187</v>
       </c>
       <c r="M11" t="s">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="N11" t="s">
-        <v>114</v>
+        <v>208</v>
       </c>
       <c r="O11" t="s">
-        <v>114</v>
+        <v>219</v>
       </c>
       <c r="P11" t="s">
-        <v>243</v>
+        <v>230</v>
       </c>
       <c r="Q11" t="s">
-        <v>197</v>
+        <v>240</v>
       </c>
       <c r="R11" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
       <c r="S11" t="s">
-        <v>197</v>
+        <v>132</v>
       </c>
       <c r="T11" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="U11" t="s">
-        <v>302</v>
+        <v>259</v>
       </c>
       <c r="V11" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="W11" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
     </row>
     <row r="12" spans="1:23">
@@ -2168,64 +2075,64 @@
         <v>78</v>
       </c>
       <c r="D12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E12" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F12" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G12" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="H12" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="I12" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="J12" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="K12" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="L12" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="M12" t="s">
+        <v>198</v>
+      </c>
+      <c r="N12" t="s">
         <v>209</v>
       </c>
-      <c r="N12" t="s">
+      <c r="O12" t="s">
         <v>220</v>
       </c>
-      <c r="O12" t="s">
-        <v>232</v>
-      </c>
       <c r="P12" t="s">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="Q12" t="s">
-        <v>256</v>
+        <v>241</v>
       </c>
       <c r="R12" t="s">
-        <v>177</v>
+        <v>251</v>
       </c>
       <c r="S12" t="s">
-        <v>279</v>
+        <v>261</v>
       </c>
       <c r="T12" t="s">
-        <v>291</v>
+        <v>270</v>
       </c>
       <c r="U12" t="s">
-        <v>303</v>
+        <v>151</v>
       </c>
       <c r="V12" t="s">
-        <v>315</v>
+        <v>288</v>
       </c>
       <c r="W12" t="s">
-        <v>326</v>
+        <v>297</v>
       </c>
     </row>
     <row r="13" spans="1:23">
@@ -2239,64 +2146,64 @@
         <v>79</v>
       </c>
       <c r="D13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E13" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F13" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="G13" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="H13" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="I13" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="J13" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="K13" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="L13" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="M13" t="s">
+        <v>199</v>
+      </c>
+      <c r="N13" t="s">
         <v>210</v>
       </c>
-      <c r="N13" t="s">
+      <c r="O13" t="s">
         <v>221</v>
       </c>
-      <c r="O13" t="s">
-        <v>233</v>
-      </c>
       <c r="P13" t="s">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="Q13" t="s">
-        <v>257</v>
+        <v>242</v>
       </c>
       <c r="R13" t="s">
-        <v>268</v>
+        <v>252</v>
       </c>
       <c r="S13" t="s">
-        <v>280</v>
+        <v>262</v>
       </c>
       <c r="T13" t="s">
-        <v>292</v>
+        <v>271</v>
       </c>
       <c r="U13" t="s">
-        <v>304</v>
+        <v>279</v>
       </c>
       <c r="V13" t="s">
-        <v>316</v>
+        <v>289</v>
       </c>
       <c r="W13" t="s">
-        <v>327</v>
+        <v>298</v>
       </c>
     </row>
     <row r="14" spans="1:23">
@@ -2309,66 +2216,6 @@
       <c r="C14" t="s">
         <v>80</v>
       </c>
-      <c r="D14">
-        <v>108.2</v>
-      </c>
-      <c r="E14">
-        <v>164.6</v>
-      </c>
-      <c r="F14">
-        <v>1024.39</v>
-      </c>
-      <c r="G14">
-        <v>1080.48</v>
-      </c>
-      <c r="H14">
-        <v>3894.41</v>
-      </c>
-      <c r="I14">
-        <v>19398.26</v>
-      </c>
-      <c r="J14">
-        <v>1323.44</v>
-      </c>
-      <c r="K14">
-        <v>261.35</v>
-      </c>
-      <c r="L14">
-        <v>512.11</v>
-      </c>
-      <c r="M14">
-        <v>175.59</v>
-      </c>
-      <c r="N14">
-        <v>164.25</v>
-      </c>
-      <c r="O14">
-        <v>154.86</v>
-      </c>
-      <c r="P14">
-        <v>139.26</v>
-      </c>
-      <c r="Q14">
-        <v>149.27</v>
-      </c>
-      <c r="R14">
-        <v>228.27</v>
-      </c>
-      <c r="S14">
-        <v>126.37</v>
-      </c>
-      <c r="T14">
-        <v>169.4</v>
-      </c>
-      <c r="U14">
-        <v>200.87</v>
-      </c>
-      <c r="V14">
-        <v>191.63</v>
-      </c>
-      <c r="W14">
-        <v>181.37</v>
-      </c>
     </row>
     <row r="15" spans="1:23">
       <c r="A15" s="1" t="s">
@@ -2381,13 +2228,13 @@
         <v>81</v>
       </c>
       <c r="D15">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="E15">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="F15">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2408,37 +2255,37 @@
         <v>0</v>
       </c>
       <c r="M15">
-        <v>7.98</v>
+        <v>0</v>
       </c>
       <c r="N15">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="O15">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="P15">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q15">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="R15">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="S15">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T15">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="U15">
-        <v>2.05</v>
+        <v>1.08</v>
       </c>
       <c r="V15">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="W15">
-        <v>2.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:23">
@@ -2452,58 +2299,64 @@
         <v>82</v>
       </c>
       <c r="D16">
-        <v>11.63</v>
+        <v>12.79</v>
       </c>
       <c r="E16">
-        <v>12.54</v>
+        <v>13.88</v>
       </c>
       <c r="F16">
-        <v>26.07</v>
+        <v>16.05</v>
+      </c>
+      <c r="G16">
+        <v>7.46</v>
+      </c>
+      <c r="H16">
+        <v>7.88</v>
       </c>
       <c r="I16">
-        <v>556</v>
+        <v>9.15</v>
       </c>
       <c r="J16">
-        <v>46.44</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="K16">
-        <v>17.3</v>
+        <v>16.89</v>
       </c>
       <c r="L16">
-        <v>42.6</v>
+        <v>13.14</v>
       </c>
       <c r="M16">
-        <v>12.85</v>
+        <v>18.2</v>
       </c>
       <c r="N16">
-        <v>14.83</v>
+        <v>18.55</v>
       </c>
       <c r="O16">
-        <v>18.92</v>
+        <v>23.16</v>
       </c>
       <c r="P16">
-        <v>9.44</v>
+        <v>18.02</v>
       </c>
       <c r="Q16">
-        <v>12.81</v>
+        <v>15.22</v>
       </c>
       <c r="R16">
-        <v>16.21</v>
+        <v>9.07</v>
       </c>
       <c r="S16">
-        <v>12.46</v>
+        <v>14.58</v>
       </c>
       <c r="T16">
-        <v>10.38</v>
+        <v>15.48</v>
       </c>
       <c r="U16">
-        <v>10.93</v>
+        <v>17.22</v>
       </c>
       <c r="V16">
-        <v>13.69</v>
+        <v>22.78</v>
       </c>
       <c r="W16">
-        <v>14.3</v>
+        <v>11.95</v>
       </c>
     </row>
     <row r="17" spans="1:23">
@@ -2517,64 +2370,64 @@
         <v>83</v>
       </c>
       <c r="D17">
-        <v>3.53</v>
+        <v>0.89</v>
       </c>
       <c r="E17">
-        <v>2.93</v>
+        <v>0.86</v>
       </c>
       <c r="F17">
-        <v>0.9</v>
+        <v>0.25</v>
       </c>
       <c r="G17">
-        <v>1.06</v>
+        <v>0.53</v>
       </c>
       <c r="H17">
-        <v>1.24</v>
+        <v>0.48</v>
       </c>
       <c r="I17">
-        <v>0.66</v>
+        <v>0.53</v>
       </c>
       <c r="J17">
-        <v>1.55</v>
+        <v>0.53</v>
       </c>
       <c r="K17">
-        <v>2.08</v>
+        <v>0.77</v>
       </c>
       <c r="L17">
-        <v>2.2</v>
+        <v>0.79</v>
       </c>
       <c r="M17">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="N17">
-        <v>2.92</v>
+        <v>0.87</v>
       </c>
       <c r="O17">
-        <v>3.65</v>
+        <v>1.23</v>
       </c>
       <c r="P17">
-        <v>2.77</v>
+        <v>0.96</v>
       </c>
       <c r="Q17">
-        <v>3.64</v>
+        <v>0.51</v>
       </c>
       <c r="R17">
-        <v>3.12</v>
+        <v>0.48</v>
       </c>
       <c r="S17">
-        <v>4.27</v>
+        <v>0.45</v>
       </c>
       <c r="T17">
-        <v>2.85</v>
+        <v>0.58</v>
       </c>
       <c r="U17">
-        <v>2.76</v>
+        <v>0.46</v>
       </c>
       <c r="V17">
-        <v>3.42</v>
+        <v>0.32</v>
       </c>
       <c r="W17">
-        <v>3.77</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="18" spans="1:23">
@@ -2588,64 +2441,64 @@
         <v>84</v>
       </c>
       <c r="D18">
-        <v>1.54</v>
+        <v>2.65</v>
       </c>
       <c r="E18">
-        <v>0.9400000000000001</v>
+        <v>2.7</v>
       </c>
       <c r="F18">
-        <v>0.23</v>
+        <v>0.72</v>
       </c>
       <c r="G18">
-        <v>0.31</v>
+        <v>3.08</v>
       </c>
       <c r="H18">
-        <v>-0.1</v>
+        <v>2.88</v>
       </c>
       <c r="I18">
-        <v>0.06999999999999999</v>
+        <v>2.61</v>
       </c>
       <c r="J18">
-        <v>0.19</v>
+        <v>3.11</v>
       </c>
       <c r="K18">
-        <v>0.53</v>
+        <v>2.73</v>
       </c>
       <c r="L18">
-        <v>0.26</v>
+        <v>3.81</v>
       </c>
       <c r="M18">
-        <v>0.75</v>
+        <v>3.71</v>
       </c>
       <c r="N18">
-        <v>0.8200000000000001</v>
+        <v>3.21</v>
       </c>
       <c r="O18">
-        <v>0.8200000000000001</v>
+        <v>3.69</v>
       </c>
       <c r="P18">
-        <v>1.21</v>
+        <v>2.45</v>
       </c>
       <c r="Q18">
-        <v>1.15</v>
+        <v>3.3</v>
       </c>
       <c r="R18">
-        <v>0.6799999999999999</v>
+        <v>5.44</v>
       </c>
       <c r="S18">
-        <v>1.07</v>
+        <v>3.46</v>
       </c>
       <c r="T18">
-        <v>0.89</v>
+        <v>4.49</v>
       </c>
       <c r="U18">
-        <v>0.8500000000000001</v>
+        <v>3.48</v>
       </c>
       <c r="V18">
-        <v>0.84</v>
+        <v>2.23</v>
       </c>
       <c r="W18">
-        <v>0.88</v>
+        <v>3.97</v>
       </c>
     </row>
     <row r="19" spans="1:23">
@@ -2659,64 +2512,64 @@
         <v>85</v>
       </c>
       <c r="D19">
-        <v>17.85</v>
+        <v>23.84</v>
       </c>
       <c r="E19">
-        <v>10.62</v>
+        <v>24.56</v>
       </c>
       <c r="F19">
-        <v>2.48</v>
+        <v>7.000000000000001</v>
       </c>
       <c r="G19">
-        <v>3.07</v>
+        <v>28.9</v>
       </c>
       <c r="H19">
-        <v>-0.97</v>
+        <v>21.21</v>
       </c>
       <c r="I19">
-        <v>0.63</v>
+        <v>17.21</v>
       </c>
       <c r="J19">
-        <v>1.79</v>
+        <v>18.27</v>
       </c>
       <c r="K19">
-        <v>4.87</v>
+        <v>14.52</v>
       </c>
       <c r="L19">
-        <v>2.32</v>
+        <v>19.7</v>
       </c>
       <c r="M19">
-        <v>6.370000000000001</v>
+        <v>18.36</v>
       </c>
       <c r="N19">
-        <v>6.819999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="O19">
-        <v>6.84</v>
+        <v>16.31</v>
       </c>
       <c r="P19">
-        <v>10.57</v>
+        <v>9.629999999999999</v>
       </c>
       <c r="Q19">
-        <v>10.35</v>
+        <v>11.82</v>
       </c>
       <c r="R19">
-        <v>6.660000000000001</v>
+        <v>17.68</v>
       </c>
       <c r="S19">
-        <v>11.78</v>
+        <v>11.02</v>
       </c>
       <c r="T19">
-        <v>10.13</v>
+        <v>14.61</v>
       </c>
       <c r="U19">
-        <v>9.390000000000001</v>
+        <v>11.36</v>
       </c>
       <c r="V19">
-        <v>9.24</v>
+        <v>7.870000000000001</v>
       </c>
       <c r="W19">
-        <v>9.94</v>
+        <v>14.97</v>
       </c>
     </row>
     <row r="20" spans="1:23">
@@ -2730,64 +2583,64 @@
         <v>86</v>
       </c>
       <c r="D20" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E20" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F20" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="G20" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="H20" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="I20" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="J20" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="K20" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="L20" t="s">
-        <v>139</v>
+        <v>190</v>
       </c>
       <c r="M20" t="s">
+        <v>200</v>
+      </c>
+      <c r="N20" t="s">
         <v>211</v>
       </c>
-      <c r="N20" t="s">
+      <c r="O20" t="s">
         <v>222</v>
       </c>
-      <c r="O20" t="s">
-        <v>234</v>
-      </c>
       <c r="P20" t="s">
-        <v>246</v>
+        <v>233</v>
       </c>
       <c r="Q20" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
       <c r="R20" t="s">
-        <v>269</v>
+        <v>253</v>
       </c>
       <c r="S20" t="s">
-        <v>281</v>
+        <v>263</v>
       </c>
       <c r="T20" t="s">
-        <v>293</v>
+        <v>272</v>
       </c>
       <c r="U20" t="s">
-        <v>305</v>
+        <v>280</v>
       </c>
       <c r="V20" t="s">
-        <v>317</v>
+        <v>290</v>
       </c>
       <c r="W20" t="s">
-        <v>328</v>
+        <v>299</v>
       </c>
     </row>
     <row r="21" spans="1:23">
@@ -2798,64 +2651,64 @@
         <v>87</v>
       </c>
       <c r="D21">
-        <v>9.210000000000001</v>
+        <v>11.68</v>
       </c>
       <c r="E21">
-        <v>9.48</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="F21">
-        <v>9.210000000000001</v>
+        <v>11.25</v>
       </c>
       <c r="G21">
-        <v>8.57</v>
+        <v>12.03</v>
       </c>
       <c r="H21">
-        <v>6.97</v>
+        <v>10.9</v>
       </c>
       <c r="I21">
-        <v>2.14</v>
+        <v>5.34</v>
       </c>
       <c r="J21">
-        <v>6.75</v>
+        <v>3.79</v>
       </c>
       <c r="K21">
-        <v>7.58</v>
+        <v>6.49</v>
       </c>
       <c r="L21">
-        <v>5.62</v>
+        <v>5.44</v>
       </c>
       <c r="M21">
-        <v>4.77</v>
+        <v>3.67</v>
       </c>
       <c r="N21">
-        <v>6.29</v>
+        <v>4.17</v>
       </c>
       <c r="O21">
-        <v>8.42</v>
+        <v>4.35</v>
       </c>
       <c r="P21">
-        <v>9.02</v>
+        <v>7.96</v>
       </c>
       <c r="Q21">
-        <v>9.51</v>
+        <v>6.5</v>
       </c>
       <c r="R21">
-        <v>6.26</v>
+        <v>5.12</v>
       </c>
       <c r="S21">
-        <v>6.63</v>
+        <v>5.64</v>
       </c>
       <c r="T21">
-        <v>8.74</v>
+        <v>6.38</v>
       </c>
       <c r="U21">
-        <v>16.73</v>
+        <v>5.35</v>
       </c>
       <c r="V21">
-        <v>18.71</v>
+        <v>5.39</v>
       </c>
       <c r="W21">
-        <v>16.74</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="22" spans="1:23">
@@ -2869,64 +2722,64 @@
         <v>88</v>
       </c>
       <c r="D22" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E22" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F22" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="G22" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="H22" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="I22" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="J22" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="K22" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="L22" t="s">
+        <v>191</v>
+      </c>
+      <c r="M22" t="s">
         <v>201</v>
       </c>
-      <c r="M22" t="s">
+      <c r="N22" t="s">
         <v>212</v>
       </c>
-      <c r="N22" t="s">
+      <c r="O22" t="s">
         <v>223</v>
       </c>
-      <c r="O22" t="s">
-        <v>235</v>
-      </c>
       <c r="P22" t="s">
-        <v>247</v>
+        <v>234</v>
       </c>
       <c r="Q22" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
       <c r="R22" t="s">
-        <v>270</v>
+        <v>254</v>
       </c>
       <c r="S22" t="s">
-        <v>282</v>
+        <v>264</v>
       </c>
       <c r="T22" t="s">
-        <v>294</v>
+        <v>273</v>
       </c>
       <c r="U22" t="s">
-        <v>306</v>
+        <v>281</v>
       </c>
       <c r="V22" t="s">
-        <v>318</v>
+        <v>229</v>
       </c>
       <c r="W22" t="s">
-        <v>329</v>
+        <v>300</v>
       </c>
     </row>
     <row r="23" spans="1:23">
@@ -2937,31 +2790,31 @@
         <v>89</v>
       </c>
       <c r="D23">
+        <v>5</v>
+      </c>
+      <c r="E23">
+        <v>7</v>
+      </c>
+      <c r="F23">
+        <v>5</v>
+      </c>
+      <c r="G23">
+        <v>5</v>
+      </c>
+      <c r="H23">
         <v>6</v>
       </c>
-      <c r="E23">
-        <v>3</v>
-      </c>
-      <c r="F23">
-        <v>4</v>
-      </c>
-      <c r="G23">
+      <c r="I23">
+        <v>5</v>
+      </c>
+      <c r="J23">
         <v>7</v>
       </c>
-      <c r="H23">
-        <v>3</v>
-      </c>
-      <c r="I23">
-        <v>7</v>
-      </c>
-      <c r="J23">
-        <v>5</v>
-      </c>
       <c r="K23">
+        <v>6</v>
+      </c>
+      <c r="L23">
         <v>8</v>
-      </c>
-      <c r="L23">
-        <v>7</v>
       </c>
       <c r="M23">
         <v>7</v>
@@ -2970,31 +2823,31 @@
         <v>7</v>
       </c>
       <c r="O23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q23">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R23">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="S23">
         <v>5</v>
       </c>
       <c r="T23">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="U23">
+        <v>5</v>
+      </c>
+      <c r="V23">
+        <v>6</v>
+      </c>
+      <c r="W23">
         <v>7</v>
-      </c>
-      <c r="V23">
-        <v>3</v>
-      </c>
-      <c r="W23">
-        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:23">
@@ -3005,64 +2858,64 @@
         <v>90</v>
       </c>
       <c r="D24">
-        <v>2.49</v>
+        <v>2.66</v>
       </c>
       <c r="E24">
-        <v>2.48</v>
+        <v>3.47</v>
       </c>
       <c r="F24">
-        <v>1.18</v>
+        <v>2.89</v>
       </c>
       <c r="G24">
-        <v>2.33</v>
+        <v>2.64</v>
       </c>
       <c r="H24">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="I24">
-        <v>2.8</v>
+        <v>1.47</v>
       </c>
       <c r="J24">
-        <v>2.25</v>
+        <v>2.58</v>
       </c>
       <c r="K24">
-        <v>2.74</v>
+        <v>2.42</v>
       </c>
       <c r="L24">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="M24">
-        <v>2.53</v>
+        <v>2.69</v>
       </c>
       <c r="N24">
-        <v>2.41</v>
+        <v>2.94</v>
       </c>
       <c r="O24">
-        <v>2.42</v>
+        <v>2.91</v>
       </c>
       <c r="P24">
-        <v>2.42</v>
+        <v>2.6</v>
       </c>
       <c r="Q24">
-        <v>2.66</v>
+        <v>4.3</v>
       </c>
       <c r="R24">
-        <v>2.43</v>
+        <v>5.68</v>
       </c>
       <c r="S24">
-        <v>2.35</v>
+        <v>6.07</v>
       </c>
       <c r="T24">
-        <v>2.48</v>
+        <v>6.6</v>
       </c>
       <c r="U24">
-        <v>2.35</v>
+        <v>6.83</v>
       </c>
       <c r="V24">
-        <v>2.4</v>
+        <v>6.46</v>
       </c>
       <c r="W24">
-        <v>2.44</v>
+        <v>7.02</v>
       </c>
     </row>
     <row r="25" spans="1:23">
@@ -3073,64 +2926,40 @@
         <v>91</v>
       </c>
       <c r="D25">
-        <v>39.38</v>
+        <v>36.48</v>
       </c>
       <c r="E25">
-        <v>26.57</v>
+        <v>44.4</v>
       </c>
       <c r="F25">
-        <v>6.21</v>
+        <v>18.58</v>
       </c>
       <c r="G25">
-        <v>6.72</v>
+        <v>118.42</v>
       </c>
       <c r="H25">
-        <v>-1.84</v>
+        <v>67.80000000000001</v>
       </c>
       <c r="I25">
-        <v>1.06</v>
+        <v>37.34</v>
       </c>
       <c r="J25">
-        <v>2.8</v>
+        <v>45.28</v>
       </c>
       <c r="K25">
-        <v>7.46</v>
+        <v>46.53</v>
       </c>
       <c r="L25">
-        <v>3.47</v>
+        <v>54.51000000000001</v>
       </c>
       <c r="M25">
-        <v>9.220000000000001</v>
+        <v>43.97</v>
       </c>
       <c r="N25">
-        <v>9.529999999999999</v>
+        <v>29.25</v>
       </c>
       <c r="O25">
-        <v>9.289999999999999</v>
-      </c>
-      <c r="P25">
-        <v>14.27</v>
-      </c>
-      <c r="Q25">
-        <v>13.99</v>
-      </c>
-      <c r="R25">
-        <v>8.949999999999999</v>
-      </c>
-      <c r="S25">
-        <v>15.79</v>
-      </c>
-      <c r="T25">
-        <v>13.59</v>
-      </c>
-      <c r="U25">
-        <v>12.43</v>
-      </c>
-      <c r="V25">
-        <v>12.08</v>
-      </c>
-      <c r="W25">
-        <v>12.93</v>
+        <v>30.81</v>
       </c>
     </row>
     <row r="26" spans="1:23">
@@ -3144,64 +2973,64 @@
         <v>92</v>
       </c>
       <c r="D26" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="E26" t="s">
-        <v>119</v>
+        <v>98</v>
       </c>
       <c r="F26" t="s">
-        <v>131</v>
+        <v>98</v>
       </c>
       <c r="G26" t="s">
-        <v>143</v>
+        <v>98</v>
       </c>
       <c r="H26" t="s">
-        <v>156</v>
+        <v>98</v>
       </c>
       <c r="I26" t="s">
-        <v>167</v>
+        <v>98</v>
       </c>
       <c r="J26" t="s">
-        <v>179</v>
+        <v>98</v>
       </c>
       <c r="K26" t="s">
-        <v>191</v>
+        <v>98</v>
       </c>
       <c r="L26" t="s">
-        <v>202</v>
+        <v>98</v>
       </c>
       <c r="M26" t="s">
-        <v>213</v>
+        <v>98</v>
       </c>
       <c r="N26" t="s">
-        <v>224</v>
+        <v>98</v>
       </c>
       <c r="O26" t="s">
-        <v>236</v>
+        <v>98</v>
       </c>
       <c r="P26" t="s">
-        <v>248</v>
+        <v>98</v>
       </c>
       <c r="Q26" t="s">
-        <v>260</v>
+        <v>98</v>
       </c>
       <c r="R26" t="s">
-        <v>271</v>
+        <v>98</v>
       </c>
       <c r="S26" t="s">
-        <v>283</v>
+        <v>98</v>
       </c>
       <c r="T26" t="s">
-        <v>295</v>
+        <v>98</v>
       </c>
       <c r="U26" t="s">
-        <v>307</v>
+        <v>98</v>
       </c>
       <c r="V26" t="s">
-        <v>319</v>
+        <v>98</v>
       </c>
       <c r="W26" t="s">
-        <v>330</v>
+        <v>98</v>
       </c>
     </row>
     <row r="27" spans="1:23">
@@ -3212,64 +3041,64 @@
         <v>93</v>
       </c>
       <c r="D27">
-        <v>0.093</v>
+        <v>0.102</v>
       </c>
       <c r="E27">
-        <v>0.08599999999999999</v>
+        <v>0.119</v>
       </c>
       <c r="F27">
-        <v>0.097</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="G27">
-        <v>0.104</v>
+        <v>0.126</v>
       </c>
       <c r="H27">
-        <v>0.101</v>
+        <v>0.145</v>
       </c>
       <c r="I27">
-        <v>0.108</v>
+        <v>0.158</v>
       </c>
       <c r="J27">
-        <v>0.107</v>
+        <v>0.182</v>
       </c>
       <c r="K27">
-        <v>0.111</v>
+        <v>0.194</v>
       </c>
       <c r="L27">
-        <v>0.116</v>
+        <v>0.193</v>
       </c>
       <c r="M27">
-        <v>0.119</v>
+        <v>0.211</v>
       </c>
       <c r="N27">
-        <v>0.122</v>
+        <v>0.231</v>
       </c>
       <c r="O27">
-        <v>0.117</v>
+        <v>0.222</v>
       </c>
       <c r="P27">
-        <v>0.113</v>
+        <v>0.268</v>
       </c>
       <c r="Q27">
-        <v>0.109</v>
+        <v>0.291</v>
       </c>
       <c r="R27">
-        <v>0.097</v>
+        <v>0.324</v>
       </c>
       <c r="S27">
-        <v>0.08500000000000001</v>
+        <v>0.304</v>
       </c>
       <c r="T27">
-        <v>0.09</v>
+        <v>0.31</v>
       </c>
       <c r="U27">
-        <v>0.092</v>
+        <v>0.303</v>
       </c>
       <c r="V27">
-        <v>0.091</v>
+        <v>0.263</v>
       </c>
       <c r="W27">
-        <v>0.089</v>
+        <v>0.265</v>
       </c>
     </row>
     <row r="28" spans="1:23">
@@ -3283,64 +3112,64 @@
         <v>94</v>
       </c>
       <c r="D28" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="E28" t="s">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="F28" t="s">
-        <v>132</v>
+        <v>98</v>
       </c>
       <c r="G28" t="s">
-        <v>144</v>
+        <v>98</v>
       </c>
       <c r="H28" t="s">
-        <v>157</v>
+        <v>98</v>
       </c>
       <c r="I28" t="s">
-        <v>168</v>
+        <v>98</v>
       </c>
       <c r="J28" t="s">
-        <v>180</v>
+        <v>98</v>
       </c>
       <c r="K28" t="s">
-        <v>192</v>
+        <v>98</v>
       </c>
       <c r="L28" t="s">
-        <v>203</v>
+        <v>98</v>
       </c>
       <c r="M28" t="s">
-        <v>214</v>
+        <v>98</v>
       </c>
       <c r="N28" t="s">
-        <v>225</v>
+        <v>98</v>
       </c>
       <c r="O28" t="s">
-        <v>237</v>
+        <v>98</v>
       </c>
       <c r="P28" t="s">
-        <v>249</v>
+        <v>98</v>
       </c>
       <c r="Q28" t="s">
-        <v>261</v>
+        <v>98</v>
       </c>
       <c r="R28" t="s">
-        <v>272</v>
+        <v>98</v>
       </c>
       <c r="S28" t="s">
-        <v>284</v>
+        <v>98</v>
       </c>
       <c r="T28" t="s">
-        <v>296</v>
+        <v>98</v>
       </c>
       <c r="U28" t="s">
-        <v>308</v>
+        <v>98</v>
       </c>
       <c r="V28" t="s">
-        <v>320</v>
+        <v>98</v>
       </c>
       <c r="W28" t="s">
-        <v>331</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
